--- a/Deliverables/BOM/Bill of Materials-John_Main.xlsx
+++ b/Deliverables/BOM/Bill of Materials-John_Main.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-MatrixProject\Design-Files\Project Outputs for John_KT\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-MatrixProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC652DF-3DB8-4EB8-857C-C31D5B20C503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125E2DA5-DCC7-4888-879A-660E0F4D49B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="303">
   <si>
     <t>Component list</t>
   </si>
@@ -677,9 +677,6 @@
     <t>Q2 , Q17, Q18, Q19, Q20, Q21, Q22, Q23, Q24, Q29, Q30, Q31, Q32, Q33, Q34, Q35, Q36, Q39, Q40, Q41, Q42, Q47, Q48, Q49, Q50, Q51, Q52, Q53, Q54, Q59, Q60, Q61, Q62, Q63, Q64, Q65, Q66, Q69, Q70, Q71, Q72, Q73, Q74, Q75, Q76</t>
   </si>
   <si>
-    <t>R1, R4, R59, R60, R61, R62, R63, R64, R65, R66, R71, R72, R73, R74, R75, R76, R77, R78, R83, R84, R85, R86, R90, R91, R92, R93, R94, R95, R96, R97, R102, R103, R104, R105, R106, R107, R108, R109, R114, R115, R116, R117, R120, R121, R122, R123, R12, R19, R20, R25, R26, RF3</t>
-  </si>
-  <si>
     <t>RP1, RP2, RP3, RP4, RP5, RP6, RP7, RP8, RP9, RP10, RP11, RP12, RP13, RP14, RP15, RP16, RP17, RP18, RP19, RP20, R3, R58</t>
   </si>
   <si>
@@ -911,19 +908,37 @@
     <t>SOD123W</t>
   </si>
   <si>
-    <t>CRS01(TE85L,Q,M)</t>
-  </si>
-  <si>
-    <t>C146292</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
-    <t xml:space="preserve">Alternate part ki specks same han footprint change ha </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Is part ka Chinies Supplier ka link ni mil raha Ap check kr len </t>
+    <t>PMEG6010ER,115</t>
+  </si>
+  <si>
+    <t>C456121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom Supplier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urooj Is part Custom supplier se Quotation le len </t>
+  </si>
+  <si>
+    <t>R12, R19, R20, R25, R26, RF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1, R4, R59, R60, R61, R62, R63, R64, R65, R66, R71, R72, R73, R74, R75, R76, R77, R78, R83, R84, R85, R86, R90, R91, R92, R93, R94, R95, R96, R97, R102, R103, R104, R105, R106, R107, R108, R109, R114, R115, R116, R117, R120, R121, R122, R123 </t>
+  </si>
+  <si>
+    <t>RES 10K OHM 5% 1/10W 0402</t>
+  </si>
+  <si>
+    <t>RK73B1ETTP103J</t>
+  </si>
+  <si>
+    <t>ERJ-2GEJ103X</t>
+  </si>
+  <si>
+    <t>C278577</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1569,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1637,43 +1652,19 @@
     <xf numFmtId="166" fontId="17" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="17" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1821,10 +1812,6 @@
     </xf>
     <xf numFmtId="166" fontId="17" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="3" borderId="32" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1858,10 +1845,41 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2201,7 +2219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U60"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -2231,8 +2249,8 @@
       <c r="G1" s="30"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="36"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="112"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
     </row>
@@ -2260,8 +2278,8 @@
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="111"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="108"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2288,7 +2306,7 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="39"/>
+      <c r="U3" s="105"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2315,7 +2333,7 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="40"/>
+      <c r="U4" s="106"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2342,7 +2360,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="40"/>
+      <c r="U5" s="106"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2365,7 +2383,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="40"/>
+      <c r="U6" s="106"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2388,199 +2406,199 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="40"/>
+      <c r="U7" s="106"/>
     </row>
     <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="54"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="40"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="106"/>
     </row>
     <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="61" t="s">
+      <c r="E9" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="64" t="s">
+      <c r="F9" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="61" t="s">
-        <v>233</v>
-      </c>
-      <c r="H9" s="64" t="s">
+      <c r="G9" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="H9" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="J9" s="64" t="s">
+      <c r="I9" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="J9" s="57" t="s">
         <v>177</v>
       </c>
-      <c r="K9" s="61" t="s">
+      <c r="K9" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="L9" s="62" t="s">
+      <c r="L9" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="M9" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="M9" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="N9" s="62" t="s">
+      <c r="N9" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="O9" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="O9" s="62" t="s">
+      <c r="P9" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q9" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="R9" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="P9" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q9" s="62" t="s">
+      <c r="S9" s="55" t="s">
         <v>226</v>
       </c>
-      <c r="R9" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="S9" s="62" t="s">
+      <c r="T9" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="T9" s="62" t="s">
-        <v>228</v>
-      </c>
-      <c r="U9" s="62" t="s">
-        <v>295</v>
+      <c r="U9" s="55" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="63">
+      <c r="B10" s="56">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="56" t="s">
+      <c r="D10" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="56" t="s">
+      <c r="E10" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="65" t="s">
+      <c r="F10" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="G10" s="72" t="s">
+      <c r="G10" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="H10" s="65" t="s">
+      <c r="H10" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="I10" s="56" t="s">
-        <v>274</v>
-      </c>
-      <c r="J10" s="65" t="s">
+      <c r="I10" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="J10" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="K10" s="93">
+      <c r="K10" s="86">
         <v>4</v>
       </c>
-      <c r="L10" s="57">
+      <c r="L10" s="50">
         <f>K10*10</f>
         <v>40</v>
       </c>
-      <c r="M10" s="57">
+      <c r="M10" s="50">
         <f>K10*100</f>
         <v>400</v>
       </c>
-      <c r="N10" s="57">
+      <c r="N10" s="50">
         <v>45</v>
       </c>
-      <c r="O10" s="57">
+      <c r="O10" s="50">
         <v>420</v>
       </c>
-      <c r="P10" s="58" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q10" s="59">
+      <c r="P10" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q10" s="52">
         <v>0.15260000000000001</v>
       </c>
-      <c r="R10" s="60">
+      <c r="R10" s="53">
         <f>Q10*N10</f>
         <v>6.8670000000000009</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="52">
         <v>0.1162</v>
       </c>
-      <c r="T10" s="60">
+      <c r="T10" s="53">
         <f>S10*O10</f>
         <v>48.804000000000002</v>
       </c>
-      <c r="U10" s="60"/>
+      <c r="U10" s="53"/>
     </row>
     <row r="11" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="63">
-        <f t="shared" ref="B11:B56" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="56">
+        <f t="shared" ref="B11:B57" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="66" t="s">
+      <c r="F11" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="I11" s="50" t="s">
-        <v>232</v>
-      </c>
-      <c r="J11" s="66" t="s">
+      <c r="I11" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="J11" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="K11" s="94">
+      <c r="K11" s="87">
         <v>14</v>
       </c>
       <c r="L11" s="32">
-        <f t="shared" ref="L11:L56" si="1">K11*10</f>
+        <f t="shared" ref="L11:L57" si="1">K11*10</f>
         <v>140</v>
       </c>
       <c r="M11" s="32">
-        <f t="shared" ref="M11:M56" si="2">K11*100</f>
+        <f t="shared" ref="M11:M57" si="2">K11*100</f>
         <v>1400</v>
       </c>
       <c r="N11" s="32">
@@ -2589,56 +2607,56 @@
       <c r="O11" s="32">
         <v>1500</v>
       </c>
-      <c r="P11" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q11" s="41">
+      <c r="P11" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q11" s="37">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="R11" s="42">
-        <f t="shared" ref="R11:R56" si="3">Q11*N11</f>
+      <c r="R11" s="38">
+        <f t="shared" ref="R11:R57" si="3">Q11*N11</f>
         <v>0.24</v>
       </c>
-      <c r="S11" s="41">
+      <c r="S11" s="37">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="T11" s="42">
-        <f t="shared" ref="T11:U56" si="4">S11*O11</f>
+      <c r="T11" s="38">
+        <f t="shared" ref="T11:T57" si="4">S11*O11</f>
         <v>1.3499999999999999</v>
       </c>
-      <c r="U11" s="42"/>
+      <c r="U11" s="38"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="63">
+      <c r="B12" s="56">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="67" t="s">
+      <c r="F12" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="H12" s="64" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="H12" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="I12" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="J12" s="71" t="s">
+      <c r="J12" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="95">
+      <c r="K12" s="88">
         <v>2</v>
       </c>
       <c r="L12" s="31">
@@ -2655,8 +2673,8 @@
       <c r="O12" s="31">
         <v>220</v>
       </c>
-      <c r="P12" s="37" t="s">
-        <v>275</v>
+      <c r="P12" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q12" s="33">
         <v>2.7099999999999999E-2</v>
@@ -2676,35 +2694,35 @@
     </row>
     <row r="13" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="63">
+      <c r="B13" s="56">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="52" t="s">
+      <c r="D13" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="F13" s="68" t="s">
+      <c r="F13" s="61" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="I13" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="J13" s="68" t="s">
+      <c r="I13" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="J13" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="K13" s="94">
+      <c r="K13" s="87">
         <v>1</v>
       </c>
       <c r="L13" s="32">
@@ -2721,56 +2739,56 @@
       <c r="O13" s="32">
         <v>110</v>
       </c>
-      <c r="P13" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q13" s="41">
+      <c r="P13" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q13" s="37">
         <v>0.53200000000000003</v>
       </c>
-      <c r="R13" s="42">
+      <c r="R13" s="38">
         <f t="shared" si="3"/>
         <v>6.3840000000000003</v>
       </c>
-      <c r="S13" s="41">
+      <c r="S13" s="37">
         <v>0.53200000000000003</v>
       </c>
-      <c r="T13" s="42">
+      <c r="T13" s="38">
         <f t="shared" si="4"/>
         <v>58.52</v>
       </c>
-      <c r="U13" s="42"/>
+      <c r="U13" s="38"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="63">
+      <c r="B14" s="56">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="67" t="s">
+      <c r="F14" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="H14" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="H14" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="J14" s="69" t="s">
+      <c r="J14" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="K14" s="95">
+      <c r="K14" s="88">
         <v>1</v>
       </c>
       <c r="L14" s="31">
@@ -2787,8 +2805,8 @@
       <c r="O14" s="31">
         <v>150</v>
       </c>
-      <c r="P14" s="37" t="s">
-        <v>275</v>
+      <c r="P14" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q14" s="33">
         <v>1.9400000000000001E-2</v>
@@ -2808,35 +2826,35 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="63">
+      <c r="B15" s="56">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="68" t="s">
+      <c r="F15" s="61" t="s">
         <v>130</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H15" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="I15" s="52" t="s">
-        <v>235</v>
-      </c>
-      <c r="J15" s="68" t="s">
+      <c r="I15" s="45" t="s">
+        <v>234</v>
+      </c>
+      <c r="J15" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="K15" s="94">
+      <c r="K15" s="87">
         <v>1</v>
       </c>
       <c r="L15" s="32">
@@ -2853,56 +2871,56 @@
       <c r="O15" s="32">
         <v>150</v>
       </c>
-      <c r="P15" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q15" s="41">
+      <c r="P15" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q15" s="37">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="R15" s="42">
+      <c r="R15" s="38">
         <f t="shared" si="3"/>
         <v>0.53499999999999992</v>
       </c>
-      <c r="S15" s="41">
+      <c r="S15" s="37">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="T15" s="42">
+      <c r="T15" s="38">
         <f t="shared" si="4"/>
         <v>1.605</v>
       </c>
-      <c r="U15" s="42"/>
+      <c r="U15" s="38"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="63">
+      <c r="B16" s="56">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="G16" s="75" t="s">
+      <c r="G16" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="I16" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="J16" s="69" t="s">
+      <c r="I16" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="J16" s="62" t="s">
         <v>184</v>
       </c>
-      <c r="K16" s="95">
+      <c r="K16" s="88">
         <v>2</v>
       </c>
       <c r="L16" s="31">
@@ -2919,8 +2937,8 @@
       <c r="O16" s="31">
         <v>210</v>
       </c>
-      <c r="P16" s="37" t="s">
-        <v>275</v>
+      <c r="P16" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q16" s="33">
         <v>0.29580000000000001</v>
@@ -2940,35 +2958,35 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="63">
+      <c r="B17" s="56">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="D17" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="E17" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="G17" s="74" t="s">
+      <c r="G17" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="61" t="s">
         <v>153</v>
       </c>
-      <c r="I17" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="J17" s="68" t="s">
+      <c r="I17" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="J17" s="61" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="94">
+      <c r="K17" s="87">
         <v>2</v>
       </c>
       <c r="L17" s="32">
@@ -2985,56 +3003,56 @@
       <c r="O17" s="32">
         <v>220</v>
       </c>
-      <c r="P17" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q17" s="41">
+      <c r="P17" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q17" s="37">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="R17" s="42">
+      <c r="R17" s="38">
         <f t="shared" si="3"/>
         <v>0.83199999999999996</v>
       </c>
-      <c r="S17" s="41">
+      <c r="S17" s="37">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="T17" s="42">
+      <c r="T17" s="38">
         <f t="shared" si="4"/>
         <v>3.6300000000000003</v>
       </c>
-      <c r="U17" s="42"/>
+      <c r="U17" s="38"/>
     </row>
     <row r="18" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="63">
+      <c r="B18" s="56">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" s="62" t="s">
         <v>208</v>
       </c>
-      <c r="G18" s="75" t="s">
+      <c r="G18" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H18" s="69" t="s">
+      <c r="H18" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="I18" s="49" t="s">
-        <v>238</v>
-      </c>
-      <c r="J18" s="69" t="s">
+      <c r="I18" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="J18" s="62" t="s">
         <v>186</v>
       </c>
-      <c r="K18" s="95">
+      <c r="K18" s="88">
         <v>2</v>
       </c>
       <c r="L18" s="31">
@@ -3051,8 +3069,8 @@
       <c r="O18" s="31">
         <v>250</v>
       </c>
-      <c r="P18" s="37" t="s">
-        <v>275</v>
+      <c r="P18" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q18" s="33">
         <v>1.03E-2</v>
@@ -3072,35 +3090,35 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="63">
+      <c r="B19" s="56">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="52" t="s">
+      <c r="D19" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="68" t="s">
+      <c r="F19" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="H19" s="68" t="s">
+      <c r="H19" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="I19" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="J19" s="68" t="s">
+      <c r="I19" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="61" t="s">
         <v>178</v>
       </c>
-      <c r="K19" s="94">
+      <c r="K19" s="87">
         <v>2</v>
       </c>
       <c r="L19" s="32">
@@ -3117,56 +3135,56 @@
       <c r="O19" s="32">
         <v>220</v>
       </c>
-      <c r="P19" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q19" s="41">
+      <c r="P19" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q19" s="37">
         <v>3.61E-2</v>
       </c>
-      <c r="R19" s="42">
+      <c r="R19" s="38">
         <f t="shared" si="3"/>
         <v>1.444</v>
       </c>
-      <c r="S19" s="41">
+      <c r="S19" s="37">
         <v>2.8799999999999999E-2</v>
       </c>
-      <c r="T19" s="42">
+      <c r="T19" s="38">
         <f t="shared" si="4"/>
         <v>6.3359999999999994</v>
       </c>
-      <c r="U19" s="42"/>
+      <c r="U19" s="38"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="63">
+      <c r="B20" s="56">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="49" t="s">
+      <c r="E20" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="62" t="s">
         <v>134</v>
       </c>
-      <c r="G20" s="75" t="s">
+      <c r="G20" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H20" s="69" t="s">
+      <c r="H20" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="I20" s="49" t="s">
-        <v>240</v>
-      </c>
-      <c r="J20" s="69" t="s">
+      <c r="I20" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="J20" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="K20" s="95">
+      <c r="K20" s="88">
         <v>1</v>
       </c>
       <c r="L20" s="31">
@@ -3183,8 +3201,8 @@
       <c r="O20" s="31">
         <v>150</v>
       </c>
-      <c r="P20" s="37" t="s">
-        <v>275</v>
+      <c r="P20" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q20" s="33">
         <v>6.4000000000000003E-3</v>
@@ -3204,35 +3222,35 @@
     </row>
     <row r="21" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="63">
+      <c r="B21" s="56">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="52" t="s">
+      <c r="E21" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="F21" s="68" t="s">
+      <c r="F21" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="G21" s="74" t="s">
+      <c r="G21" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="H21" s="68" t="s">
+      <c r="H21" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I21" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="J21" s="68" t="s">
+      <c r="I21" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="J21" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="K21" s="94">
+      <c r="K21" s="87">
         <v>1</v>
       </c>
       <c r="L21" s="32">
@@ -3249,56 +3267,56 @@
       <c r="O21" s="32">
         <v>200</v>
       </c>
-      <c r="P21" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q21" s="41">
+      <c r="P21" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q21" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R21" s="42">
+      <c r="R21" s="38">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="S21" s="41">
+      <c r="S21" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T21" s="42">
+      <c r="T21" s="38">
         <f t="shared" si="4"/>
         <v>0.26</v>
       </c>
-      <c r="U21" s="42"/>
+      <c r="U21" s="38"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="63">
+      <c r="B22" s="56">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="49" t="s">
+      <c r="E22" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="67" t="s">
+      <c r="F22" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="G22" s="49" t="s">
+      <c r="G22" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="H22" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="H22" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>271</v>
-      </c>
-      <c r="J22" s="69" t="s">
+      <c r="J22" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="K22" s="95">
+      <c r="K22" s="88">
         <v>2</v>
       </c>
       <c r="L22" s="31">
@@ -3315,8 +3333,8 @@
       <c r="O22" s="31">
         <v>300</v>
       </c>
-      <c r="P22" s="37" t="s">
-        <v>275</v>
+      <c r="P22" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q22" s="33">
         <v>1.2999999999999999E-3</v>
@@ -3336,35 +3354,35 @@
     </row>
     <row r="23" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="63">
+      <c r="B23" s="56">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="52" t="s">
+      <c r="D23" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="E23" s="52" t="s">
-        <v>292</v>
-      </c>
-      <c r="F23" s="70" t="s">
+      <c r="E23" s="45" t="s">
+        <v>291</v>
+      </c>
+      <c r="F23" s="63" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="52" t="s">
+      <c r="G23" s="45" t="s">
         <v>293</v>
       </c>
-      <c r="H23" s="68" t="s">
+      <c r="H23" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="I23" s="52" t="s">
+      <c r="I23" s="45" t="s">
         <v>294</v>
       </c>
-      <c r="J23" s="91" t="s">
+      <c r="J23" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="K23" s="94">
+      <c r="K23" s="87">
         <v>2</v>
       </c>
       <c r="L23" s="32">
@@ -3381,58 +3399,56 @@
       <c r="O23" s="32">
         <v>210</v>
       </c>
-      <c r="P23" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q23" s="41">
-        <v>0.1595</v>
-      </c>
-      <c r="R23" s="42">
+      <c r="P23" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q23" s="37">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="R23" s="38">
         <f t="shared" si="3"/>
-        <v>3.5089999999999999</v>
-      </c>
-      <c r="S23" s="41">
-        <v>0.13550000000000001</v>
-      </c>
-      <c r="T23" s="42">
+        <v>3.6387999999999998</v>
+      </c>
+      <c r="S23" s="37">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="T23" s="38">
         <f t="shared" si="4"/>
-        <v>28.455000000000002</v>
-      </c>
-      <c r="U23" s="108" t="s">
-        <v>296</v>
-      </c>
+        <v>28.665000000000003</v>
+      </c>
+      <c r="U23" s="100"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
-      <c r="B24" s="63">
+      <c r="B24" s="56">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="49">
+      <c r="E24" s="42">
         <v>1812</v>
       </c>
-      <c r="F24" s="69" t="s">
+      <c r="F24" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H24" s="69" t="s">
+      <c r="H24" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="I24" s="49" t="s">
-        <v>242</v>
-      </c>
-      <c r="J24" s="90" t="s">
+      <c r="I24" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="J24" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="K24" s="95">
+      <c r="K24" s="88">
         <v>1</v>
       </c>
       <c r="L24" s="31">
@@ -3449,8 +3465,8 @@
       <c r="O24" s="31">
         <v>110</v>
       </c>
-      <c r="P24" s="37" t="s">
-        <v>275</v>
+      <c r="P24" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q24" s="33">
         <v>0.15989999999999999</v>
@@ -3470,35 +3486,35 @@
     </row>
     <row r="25" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="63">
+      <c r="B25" s="56">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="F25" s="61" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="I25" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="F25" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="G25" s="74" t="s">
+      <c r="J25" s="84" t="s">
         <v>212</v>
       </c>
-      <c r="H25" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="I25" s="52" t="s">
-        <v>244</v>
-      </c>
-      <c r="J25" s="91" t="s">
-        <v>212</v>
-      </c>
-      <c r="K25" s="94">
+      <c r="K25" s="87">
         <v>1</v>
       </c>
       <c r="L25" s="32">
@@ -3515,56 +3531,56 @@
       <c r="O25" s="32">
         <v>120</v>
       </c>
-      <c r="P25" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q25" s="41">
+      <c r="P25" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q25" s="37">
         <v>4.53E-2</v>
       </c>
-      <c r="R25" s="42">
+      <c r="R25" s="38">
         <f t="shared" si="3"/>
         <v>0.90600000000000003</v>
       </c>
-      <c r="S25" s="41">
+      <c r="S25" s="37">
         <v>4.53E-2</v>
       </c>
-      <c r="T25" s="42">
+      <c r="T25" s="38">
         <f t="shared" si="4"/>
         <v>5.4359999999999999</v>
       </c>
-      <c r="U25" s="42"/>
+      <c r="U25" s="38"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="63">
+      <c r="B26" s="56">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="E26" s="49" t="s">
+      <c r="E26" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F26" s="69" t="s">
+      <c r="F26" s="62" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="75" t="s">
+      <c r="G26" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H26" s="90" t="s">
+      <c r="H26" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="I26" s="75" t="s">
+      <c r="I26" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="J26" s="90" t="s">
+      <c r="J26" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="K26" s="95">
+      <c r="K26" s="88">
         <v>7</v>
       </c>
       <c r="L26" s="31">
@@ -3575,52 +3591,60 @@
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="N26" s="31"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="34">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
+      <c r="N26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="O26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="P26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="R26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="S26" s="113" t="s">
+        <v>209</v>
+      </c>
+      <c r="T26" s="113" t="s">
+        <v>209</v>
       </c>
       <c r="U26" s="34"/>
     </row>
     <row r="27" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="63">
+      <c r="B27" s="56">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="52" t="s">
+      <c r="E27" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="F27" s="70">
+      <c r="F27" s="63">
         <v>1729225</v>
       </c>
-      <c r="G27" s="52" t="s">
+      <c r="G27" s="45" t="s">
+        <v>285</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="H27" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="52" t="s">
-        <v>287</v>
-      </c>
-      <c r="J27" s="91" t="s">
+      <c r="J27" s="84" t="s">
         <v>212</v>
       </c>
-      <c r="K27" s="94">
+      <c r="K27" s="87">
         <v>1</v>
       </c>
       <c r="L27" s="32">
@@ -3637,56 +3661,56 @@
       <c r="O27" s="32">
         <v>105</v>
       </c>
-      <c r="P27" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q27" s="41">
+      <c r="P27" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q27" s="37">
         <v>0.64739999999999998</v>
       </c>
-      <c r="R27" s="42">
+      <c r="R27" s="38">
         <f t="shared" si="3"/>
         <v>7.7687999999999997</v>
       </c>
-      <c r="S27" s="41">
+      <c r="S27" s="37">
         <v>0.53559999999999997</v>
       </c>
-      <c r="T27" s="42">
+      <c r="T27" s="38">
         <f t="shared" si="4"/>
         <v>56.238</v>
       </c>
-      <c r="U27" s="42"/>
+      <c r="U27" s="38"/>
     </row>
     <row r="28" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="63">
+      <c r="B28" s="56">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="69" t="s">
+      <c r="F28" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="G28" s="75" t="s">
+      <c r="G28" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H28" s="69" t="s">
+      <c r="H28" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="I28" s="49" t="s">
+      <c r="I28" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="J28" s="83" t="s">
         <v>245</v>
       </c>
-      <c r="J28" s="90" t="s">
-        <v>246</v>
-      </c>
-      <c r="K28" s="95">
+      <c r="K28" s="88">
         <v>1</v>
       </c>
       <c r="L28" s="31">
@@ -3703,8 +3727,8 @@
       <c r="O28" s="31">
         <v>110</v>
       </c>
-      <c r="P28" s="37" t="s">
-        <v>275</v>
+      <c r="P28" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q28" s="33">
         <v>0.1855</v>
@@ -3724,35 +3748,35 @@
     </row>
     <row r="29" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="63">
+      <c r="B29" s="56">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="52" t="s">
+      <c r="D29" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="52" t="s">
-        <v>276</v>
-      </c>
-      <c r="F29" s="68" t="s">
+      <c r="E29" s="45" t="s">
+        <v>275</v>
+      </c>
+      <c r="F29" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="G29" s="74" t="s">
+      <c r="G29" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="H29" s="68" t="s">
+      <c r="H29" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="I29" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="J29" s="91" t="s">
+      <c r="I29" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="J29" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="K29" s="94">
+      <c r="K29" s="87">
         <v>22</v>
       </c>
       <c r="L29" s="32">
@@ -3769,54 +3793,54 @@
       <c r="O29" s="32">
         <v>2260</v>
       </c>
-      <c r="P29" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q29" s="41">
+      <c r="P29" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q29" s="37">
         <v>1.55E-2</v>
       </c>
-      <c r="R29" s="42">
+      <c r="R29" s="38">
         <f t="shared" si="3"/>
         <v>3.7199999999999998</v>
       </c>
-      <c r="S29" s="41">
+      <c r="S29" s="37">
         <v>1.18E-2</v>
       </c>
-      <c r="T29" s="42">
+      <c r="T29" s="38">
         <f t="shared" si="4"/>
         <v>26.667999999999999</v>
       </c>
-      <c r="U29" s="42"/>
+      <c r="U29" s="38"/>
     </row>
     <row r="30" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="63">
+      <c r="B30" s="56">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="49" t="s">
+      <c r="E30" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F30" s="69" t="s">
+      <c r="F30" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="G30" s="75" t="s">
+      <c r="G30" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="H30" s="69" t="s">
+      <c r="H30" s="62" t="s">
         <v>164</v>
       </c>
-      <c r="I30" s="49"/>
-      <c r="J30" s="69" t="s">
+      <c r="I30" s="42"/>
+      <c r="J30" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="K30" s="95">
+      <c r="K30" s="88">
         <v>1</v>
       </c>
       <c r="L30" s="31">
@@ -3833,8 +3857,8 @@
       <c r="O30" s="31">
         <v>110</v>
       </c>
-      <c r="P30" s="37" t="s">
-        <v>273</v>
+      <c r="P30" s="35" t="s">
+        <v>272</v>
       </c>
       <c r="Q30" s="33">
         <v>0.38900000000000001</v>
@@ -3854,29 +3878,29 @@
     </row>
     <row r="31" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="63">
+      <c r="B31" s="56">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="F31" s="68">
+      <c r="F31" s="61">
         <v>22232111</v>
       </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="68" t="s">
+      <c r="G31" s="45"/>
+      <c r="H31" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="I31" s="52"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="94">
+      <c r="I31" s="45"/>
+      <c r="J31" s="61"/>
+      <c r="K31" s="87">
         <v>2</v>
       </c>
       <c r="L31" s="32">
@@ -3887,54 +3911,60 @@
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="41"/>
-      <c r="R31" s="42">
+      <c r="N31" s="32">
+        <v>22</v>
+      </c>
+      <c r="O31" s="32">
+        <v>205</v>
+      </c>
+      <c r="P31" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="38">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S31" s="41"/>
-      <c r="T31" s="42">
+      <c r="S31" s="37"/>
+      <c r="T31" s="38">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U31" s="108" t="s">
-        <v>297</v>
+      <c r="U31" s="100" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="63">
+      <c r="B32" s="56">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="49" t="s">
+      <c r="E32" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="69" t="s">
+      <c r="F32" s="62" t="s">
         <v>190</v>
       </c>
-      <c r="G32" s="75" t="s">
+      <c r="G32" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="H32" s="69" t="s">
+      <c r="H32" s="62" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="75" t="s">
+      <c r="I32" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="J32" s="90" t="s">
+      <c r="J32" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="K32" s="95">
+      <c r="K32" s="88">
         <v>1</v>
       </c>
       <c r="L32" s="31">
@@ -3951,8 +3981,8 @@
       <c r="O32" s="31">
         <v>275</v>
       </c>
-      <c r="P32" s="37" t="s">
-        <v>277</v>
+      <c r="P32" s="35" t="s">
+        <v>276</v>
       </c>
       <c r="Q32" s="33">
         <v>0.184</v>
@@ -3972,35 +4002,35 @@
     </row>
     <row r="33" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="63">
+      <c r="B33" s="56">
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="49" t="s">
+      <c r="E33" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="69" t="s">
+      <c r="F33" s="62" t="s">
         <v>138</v>
       </c>
-      <c r="G33" s="75" t="s">
+      <c r="G33" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H33" s="69" t="s">
+      <c r="H33" s="62" t="s">
         <v>168</v>
       </c>
-      <c r="I33" s="75" t="s">
+      <c r="I33" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="J33" s="90" t="s">
+      <c r="J33" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="K33" s="95">
+      <c r="K33" s="88">
         <v>20</v>
       </c>
       <c r="L33" s="31">
@@ -4017,8 +4047,8 @@
       <c r="O33" s="31">
         <v>2000</v>
       </c>
-      <c r="P33" s="37" t="s">
-        <v>273</v>
+      <c r="P33" s="35" t="s">
+        <v>272</v>
       </c>
       <c r="Q33" s="33">
         <v>3.9800000000000002E-2</v>
@@ -4038,35 +4068,35 @@
     </row>
     <row r="34" spans="1:21" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="63">
+      <c r="B34" s="56">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="43" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="50" t="s">
+      <c r="D34" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="50" t="s">
+      <c r="E34" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="66" t="s">
+      <c r="F34" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="73" t="s">
+      <c r="G34" s="66" t="s">
         <v>210</v>
       </c>
-      <c r="H34" s="66" t="s">
+      <c r="H34" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="J34" s="92" t="s">
+      <c r="I34" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="J34" s="85" t="s">
         <v>209</v>
       </c>
-      <c r="K34" s="94">
+      <c r="K34" s="87">
         <v>45</v>
       </c>
       <c r="L34" s="32">
@@ -4083,1582 +4113,1647 @@
       <c r="O34" s="32">
         <v>4600</v>
       </c>
-      <c r="P34" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q34" s="41">
+      <c r="P34" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q34" s="37">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="R34" s="42">
+      <c r="R34" s="38">
         <f t="shared" si="3"/>
         <v>3.75</v>
       </c>
-      <c r="S34" s="41">
+      <c r="S34" s="37">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="T34" s="42">
+      <c r="T34" s="38">
         <f t="shared" si="4"/>
         <v>34.5</v>
       </c>
-      <c r="U34" s="42"/>
-    </row>
-    <row r="35" spans="1:21" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="U34" s="38"/>
+    </row>
+    <row r="35" spans="1:21" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="63">
+      <c r="B35" s="56">
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="D35" s="51" t="s">
+      <c r="C35" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="D35" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E35" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="71" t="s">
+      <c r="F35" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="G35" s="76" t="s">
+      <c r="G35" s="69" t="s">
         <v>212</v>
       </c>
-      <c r="H35" s="71" t="s">
+      <c r="H35" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="I35" s="51" t="s">
-        <v>249</v>
-      </c>
-      <c r="J35" s="71" t="s">
+      <c r="I35" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="J35" s="64" t="s">
         <v>191</v>
       </c>
-      <c r="K35" s="95">
-        <v>52</v>
+      <c r="K35" s="88">
+        <v>46</v>
       </c>
       <c r="L35" s="31">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>460</v>
       </c>
       <c r="M35" s="31">
         <f t="shared" si="2"/>
-        <v>5200</v>
+        <v>4600</v>
       </c>
       <c r="N35" s="31">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="O35" s="31">
-        <v>5300</v>
-      </c>
-      <c r="P35" s="37" t="s">
-        <v>275</v>
+        <v>4700</v>
+      </c>
+      <c r="P35" s="35" t="s">
+        <v>274</v>
       </c>
       <c r="Q35" s="33">
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="R35" s="34">
         <f t="shared" si="3"/>
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="S35" s="33">
         <v>4.0000000000000002E-4</v>
       </c>
       <c r="T35" s="34">
         <f t="shared" si="4"/>
-        <v>2.12</v>
+        <v>1.8800000000000001</v>
       </c>
       <c r="U35" s="34"/>
     </row>
-    <row r="36" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="63">
+      <c r="B36" s="56">
+        <v>27</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F36" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="G36" s="69" t="s">
+        <v>301</v>
+      </c>
+      <c r="H36" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="J36" s="64" t="s">
+        <v>191</v>
+      </c>
+      <c r="K36" s="88">
+        <v>6</v>
+      </c>
+      <c r="L36" s="31">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="M36" s="31">
+        <f t="shared" si="2"/>
+        <v>600</v>
+      </c>
+      <c r="N36" s="31">
+        <v>100</v>
+      </c>
+      <c r="O36" s="31">
+        <v>700</v>
+      </c>
+      <c r="P36" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q36" s="33">
+        <v>4.3E-3</v>
+      </c>
+      <c r="R36" s="34">
+        <f t="shared" si="3"/>
+        <v>0.43</v>
+      </c>
+      <c r="S36" s="33">
+        <v>4.3E-3</v>
+      </c>
+      <c r="T36" s="34">
+        <f t="shared" si="4"/>
+        <v>3.01</v>
+      </c>
+      <c r="U36" s="34"/>
+    </row>
+    <row r="37" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="56">
         <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="52" t="s">
+      <c r="D37" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="52" t="s">
+      <c r="E37" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F36" s="68" t="s">
+      <c r="F37" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="G36" s="74" t="s">
+      <c r="G37" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="H36" s="68" t="s">
+      <c r="H37" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I36" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="J36" s="68" t="s">
+      <c r="I37" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="J37" s="61" t="s">
         <v>192</v>
       </c>
-      <c r="K36" s="94">
+      <c r="K37" s="87">
         <v>1</v>
       </c>
-      <c r="L36" s="32">
+      <c r="L37" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M37" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N36" s="32">
+      <c r="N37" s="32">
         <v>100</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O37" s="32">
         <v>200</v>
       </c>
-      <c r="P36" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q36" s="41">
+      <c r="P37" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q37" s="37">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="R36" s="42">
+      <c r="R37" s="38">
         <f t="shared" si="3"/>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="S36" s="41">
+      <c r="S37" s="37">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="T36" s="42">
+      <c r="T37" s="38">
         <f t="shared" si="4"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="U36" s="42"/>
-    </row>
-    <row r="37" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="63">
+      <c r="U37" s="38"/>
+    </row>
+    <row r="38" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="56">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="D38" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E38" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="F37" s="66" t="s">
+      <c r="F38" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="G37" s="73" t="s">
+      <c r="G38" s="66" t="s">
         <v>212</v>
       </c>
-      <c r="H37" s="66" t="s">
+      <c r="H38" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="I37" s="50" t="s">
-        <v>251</v>
-      </c>
-      <c r="J37" s="66" t="s">
+      <c r="I38" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="J38" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="K37" s="94">
+      <c r="K38" s="87">
         <v>5</v>
       </c>
-      <c r="L37" s="32">
+      <c r="L38" s="32">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M37" s="32">
+      <c r="M38" s="32">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N37" s="32">
+      <c r="N38" s="32">
         <v>100</v>
       </c>
-      <c r="O37" s="32">
+      <c r="O38" s="32">
         <v>600</v>
       </c>
-      <c r="P37" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q37" s="41">
+      <c r="P38" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q38" s="37">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="R37" s="42">
+      <c r="R38" s="38">
         <f t="shared" si="3"/>
         <v>0.12</v>
       </c>
-      <c r="S37" s="41">
+      <c r="S38" s="37">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="T37" s="42">
+      <c r="T38" s="38">
         <f t="shared" si="4"/>
         <v>0.72</v>
       </c>
-      <c r="U37" s="42"/>
-    </row>
-    <row r="38" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="63">
-        <f>ROW(B38) - ROW($B$9)</f>
-        <v>29</v>
-      </c>
-      <c r="C38" s="49" t="s">
+      <c r="U38" s="38"/>
+    </row>
+    <row r="39" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="56">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D38" s="49" t="s">
+      <c r="D39" s="42" t="s">
         <v>83</v>
       </c>
-      <c r="E38" s="49" t="s">
+      <c r="E39" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="F38" s="69" t="s">
+      <c r="F39" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="G38" s="75" t="s">
+      <c r="G39" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H38" s="69" t="s">
+      <c r="H39" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="I38" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="J38" s="69" t="s">
+      <c r="I39" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="J39" s="62" t="s">
         <v>195</v>
       </c>
-      <c r="K38" s="95">
+      <c r="K39" s="88">
         <v>1</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L39" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M39" s="31">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N39" s="31">
         <v>100</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O39" s="31">
         <v>200</v>
       </c>
-      <c r="P38" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q38" s="33">
+      <c r="P39" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q39" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R39" s="34">
         <f t="shared" si="3"/>
         <v>0.08</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S39" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T39" s="34">
         <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="U38" s="34"/>
-    </row>
-    <row r="39" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="63">
+      <c r="U39" s="34"/>
+    </row>
+    <row r="40" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="56">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="52" t="s">
+      <c r="D40" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="E39" s="52" t="s">
+      <c r="E40" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F39" s="68" t="s">
+      <c r="F40" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="74" t="s">
+      <c r="G40" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="H39" s="68" t="s">
+      <c r="H40" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I39" s="52" t="s">
-        <v>253</v>
-      </c>
-      <c r="J39" s="68" t="s">
+      <c r="I40" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="J40" s="61" t="s">
         <v>196</v>
       </c>
-      <c r="K39" s="94">
+      <c r="K40" s="87">
         <v>2</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L40" s="32">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M40" s="32">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N40" s="32">
         <v>100</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O40" s="32">
         <v>300</v>
       </c>
-      <c r="P39" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q39" s="41">
+      <c r="P40" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q40" s="37">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="R39" s="42">
+      <c r="R40" s="38">
         <f t="shared" si="3"/>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="S39" s="41">
+      <c r="S40" s="37">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="T39" s="42">
+      <c r="T40" s="38">
         <f t="shared" si="4"/>
         <v>0.21</v>
       </c>
-      <c r="U39" s="42"/>
-    </row>
-    <row r="40" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="63">
-        <f>ROW(B40) - ROW($B$9)</f>
-        <v>31</v>
-      </c>
-      <c r="C40" s="49" t="s">
+      <c r="U40" s="38"/>
+    </row>
+    <row r="41" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="56">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="49" t="s">
+      <c r="D41" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="E40" s="49" t="s">
+      <c r="E41" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="69" t="s">
+      <c r="F41" s="62" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="75" t="s">
+      <c r="G41" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H40" s="69" t="s">
+      <c r="H41" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="I40" s="49" t="s">
-        <v>254</v>
-      </c>
-      <c r="J40" s="69" t="s">
+      <c r="I41" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="J41" s="62" t="s">
         <v>197</v>
       </c>
-      <c r="K40" s="95">
+      <c r="K41" s="88">
         <v>1</v>
       </c>
-      <c r="L40" s="31">
+      <c r="L41" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M40" s="31">
+      <c r="M41" s="31">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N40" s="31">
+      <c r="N41" s="31">
         <v>100</v>
       </c>
-      <c r="O40" s="31">
+      <c r="O41" s="31">
         <v>200</v>
       </c>
-      <c r="P40" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q40" s="33">
+      <c r="P41" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q41" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R40" s="34">
+      <c r="R41" s="34">
         <f t="shared" si="3"/>
         <v>0.08</v>
       </c>
-      <c r="S40" s="33">
+      <c r="S41" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T40" s="34">
+      <c r="T41" s="34">
         <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="U40" s="34"/>
-    </row>
-    <row r="41" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="63">
+      <c r="U41" s="34"/>
+    </row>
+    <row r="42" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="56">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="52" t="s">
+      <c r="D42" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="52" t="s">
+      <c r="E42" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="F42" s="61" t="s">
         <v>145</v>
       </c>
-      <c r="G41" s="74" t="s">
+      <c r="G42" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="H42" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I41" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="J41" s="68" t="s">
+      <c r="I42" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="J42" s="61" t="s">
         <v>198</v>
       </c>
-      <c r="K41" s="94">
+      <c r="K42" s="87">
         <v>1</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L42" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M42" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N42" s="32">
         <v>100</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O42" s="32">
         <v>200</v>
       </c>
-      <c r="P41" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q41" s="41">
+      <c r="P42" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q42" s="37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R41" s="42">
+      <c r="R42" s="38">
         <f t="shared" si="3"/>
         <v>0.08</v>
       </c>
-      <c r="S41" s="41">
+      <c r="S42" s="37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T41" s="42">
+      <c r="T42" s="38">
         <f t="shared" si="4"/>
         <v>0.16</v>
       </c>
-      <c r="U41" s="42"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="63">
-        <f>ROW(B42) - ROW($B$9)</f>
-        <v>33</v>
-      </c>
-      <c r="C42" s="49" t="s">
+      <c r="U42" s="38"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="56">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="49" t="s">
+      <c r="D43" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="E42" s="49" t="s">
+      <c r="E43" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="F42" s="67" t="s">
+      <c r="F43" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G43" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="H43" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="H42" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="I42" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="J42" s="69" t="s">
+      <c r="J43" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="K42" s="95">
+      <c r="K43" s="88">
         <v>5</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L43" s="31">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M43" s="31">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N43" s="31">
         <v>100</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O43" s="31">
         <v>600</v>
       </c>
-      <c r="P42" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q42" s="33">
+      <c r="P43" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q43" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R43" s="34">
         <f t="shared" si="3"/>
         <v>0.08</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S43" s="33">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T43" s="34">
         <f t="shared" si="4"/>
         <v>0.48000000000000004</v>
       </c>
-      <c r="U42" s="34"/>
-    </row>
-    <row r="43" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="63">
-        <f>ROW(B43) - ROW($B$9)</f>
-        <v>34</v>
-      </c>
-      <c r="C43" s="49" t="s">
+      <c r="U43" s="34"/>
+    </row>
+    <row r="44" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="56">
+        <f>ROW(B44) - ROW($B$9)</f>
+        <v>35</v>
+      </c>
+      <c r="C44" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="49" t="s">
+      <c r="D44" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="E43" s="49" t="s">
+      <c r="E44" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="F43" s="67" t="s">
-        <v>217</v>
-      </c>
-      <c r="G43" s="49" t="s">
+      <c r="F44" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="H44" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="42" t="s">
         <v>280</v>
       </c>
-      <c r="H43" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="I43" s="49" t="s">
-        <v>281</v>
-      </c>
-      <c r="J43" s="69" t="s">
+      <c r="J44" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="K43" s="95">
+      <c r="K44" s="88">
         <v>2</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L44" s="31">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M44" s="31">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N43" s="31">
+      <c r="N44" s="31">
         <v>100</v>
       </c>
-      <c r="O43" s="31">
+      <c r="O44" s="31">
         <v>300</v>
       </c>
-      <c r="P43" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q43" s="33">
+      <c r="P44" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q44" s="33">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="R43" s="34">
+      <c r="R44" s="34">
         <f t="shared" si="3"/>
         <v>0.06</v>
       </c>
-      <c r="S43" s="33">
+      <c r="S44" s="33">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="T43" s="34">
+      <c r="T44" s="34">
         <f t="shared" si="4"/>
         <v>0.18</v>
       </c>
-      <c r="U43" s="34"/>
-    </row>
-    <row r="44" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="63">
+      <c r="U44" s="34"/>
+    </row>
+    <row r="45" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="56">
         <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D44" s="52" t="s">
+      <c r="D45" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="E44" s="52" t="s">
+      <c r="E45" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F44" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="G44" s="74" t="s">
+      <c r="F45" s="61" t="s">
+        <v>217</v>
+      </c>
+      <c r="G45" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="68" t="s">
+      <c r="H45" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I44" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="J44" s="68" t="s">
+      <c r="I45" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="J45" s="61" t="s">
         <v>201</v>
       </c>
-      <c r="K44" s="94">
+      <c r="K45" s="87">
         <v>4</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L45" s="32">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M45" s="32">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N45" s="32">
         <v>100</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O45" s="32">
         <v>500</v>
       </c>
-      <c r="P44" s="32"/>
-      <c r="Q44" s="41">
+      <c r="P45" s="32"/>
+      <c r="Q45" s="37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R44" s="42">
+      <c r="R45" s="38">
         <f t="shared" si="3"/>
         <v>0.08</v>
       </c>
-      <c r="S44" s="41">
+      <c r="S45" s="37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T44" s="42">
+      <c r="T45" s="38">
         <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
-      <c r="U44" s="42"/>
-    </row>
-    <row r="45" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="63">
-        <f>ROW(B45) - ROW($B$9)</f>
-        <v>36</v>
-      </c>
-      <c r="C45" s="51" t="s">
+      <c r="U45" s="38"/>
+    </row>
+    <row r="46" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="56">
+        <f>ROW(B46) - ROW($B$9)</f>
+        <v>37</v>
+      </c>
+      <c r="C46" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="51" t="s">
+      <c r="D46" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="51" t="s">
+      <c r="E46" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="F45" s="71" t="s">
+      <c r="F46" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="G45" s="76" t="s">
+      <c r="G46" s="69" t="s">
         <v>209</v>
       </c>
-      <c r="H45" s="71" t="s">
+      <c r="H46" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="I45" s="51" t="s">
-        <v>257</v>
-      </c>
-      <c r="J45" s="71" t="s">
+      <c r="I46" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="J46" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="K45" s="95">
+      <c r="K46" s="88">
         <v>20</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L46" s="31">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M46" s="31">
         <f t="shared" si="2"/>
         <v>2000</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N46" s="31">
         <v>300</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O46" s="31">
         <v>2100</v>
       </c>
-      <c r="P45" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q45" s="33">
+      <c r="P46" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q46" s="33">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R46" s="34">
         <f t="shared" si="3"/>
         <v>0.27</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S46" s="33">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T46" s="34">
         <f t="shared" si="4"/>
         <v>1.47</v>
       </c>
-      <c r="U45" s="34"/>
-    </row>
-    <row r="46" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="63">
+      <c r="U46" s="34"/>
+    </row>
+    <row r="47" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="56">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="52" t="s">
+      <c r="D47" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E46" s="52" t="s">
+      <c r="E47" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F46" s="68" t="s">
+      <c r="F47" s="61" t="s">
         <v>148</v>
       </c>
-      <c r="G46" s="74" t="s">
+      <c r="G47" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="H46" s="68" t="s">
+      <c r="H47" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I46" s="52" t="s">
-        <v>258</v>
-      </c>
-      <c r="J46" s="68" t="s">
+      <c r="I47" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="J47" s="61" t="s">
         <v>203</v>
       </c>
-      <c r="K46" s="94">
+      <c r="K47" s="87">
         <v>1</v>
       </c>
-      <c r="L46" s="32">
+      <c r="L47" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M46" s="32">
+      <c r="M47" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N46" s="32">
+      <c r="N47" s="32">
         <v>100</v>
       </c>
-      <c r="O46" s="32">
+      <c r="O47" s="32">
         <v>200</v>
       </c>
-      <c r="P46" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q46" s="41">
+      <c r="P47" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q47" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="R46" s="42">
+      <c r="R47" s="38">
         <f t="shared" si="3"/>
         <v>0.13</v>
       </c>
-      <c r="S46" s="41">
+      <c r="S47" s="37">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="T46" s="42">
+      <c r="T47" s="38">
         <f t="shared" si="4"/>
         <v>0.26</v>
       </c>
-      <c r="U46" s="42"/>
-    </row>
-    <row r="47" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="63">
-        <f>ROW(B47) - ROW($B$9)</f>
-        <v>38</v>
-      </c>
-      <c r="C47" s="49" t="s">
+      <c r="U47" s="38"/>
+    </row>
+    <row r="48" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="56">
+        <f>ROW(B48) - ROW($B$9)</f>
+        <v>39</v>
+      </c>
+      <c r="C48" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D47" s="49" t="s">
+      <c r="D48" s="42" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="49" t="s">
+      <c r="E48" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="F47" s="69" t="s">
+      <c r="F48" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="G47" s="75" t="s">
+      <c r="G48" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="H47" s="69" t="s">
+      <c r="H48" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="I47" s="49" t="s">
-        <v>259</v>
-      </c>
-      <c r="J47" s="69" t="s">
+      <c r="I48" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="J48" s="62" t="s">
         <v>204</v>
       </c>
-      <c r="K47" s="95">
+      <c r="K48" s="88">
         <v>4</v>
       </c>
-      <c r="L47" s="31">
+      <c r="L48" s="31">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="M47" s="31">
+      <c r="M48" s="31">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="N47" s="31">
+      <c r="N48" s="31">
         <v>100</v>
       </c>
-      <c r="O47" s="31">
+      <c r="O48" s="31">
         <v>500</v>
       </c>
-      <c r="P47" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q47" s="33">
+      <c r="P48" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q48" s="33">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="R47" s="34">
+      <c r="R48" s="34">
         <f t="shared" si="3"/>
         <v>0.24</v>
       </c>
-      <c r="S47" s="33">
+      <c r="S48" s="33">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T48" s="34">
         <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
-      <c r="U47" s="34"/>
-    </row>
-    <row r="48" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="63">
+      <c r="U48" s="34"/>
+    </row>
+    <row r="49" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="56">
         <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="D48" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="D49" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E49" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="F48" s="70" t="s">
+      <c r="F49" s="63" t="s">
         <v>150</v>
       </c>
-      <c r="G48" s="50" t="s">
+      <c r="G49" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="H49" s="59" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="43" t="s">
         <v>282</v>
       </c>
-      <c r="H48" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="I48" s="50" t="s">
-        <v>283</v>
-      </c>
-      <c r="J48" s="66" t="s">
+      <c r="J49" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="K48" s="94">
+      <c r="K49" s="87">
         <v>22</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L49" s="32">
         <f t="shared" si="1"/>
         <v>220</v>
       </c>
-      <c r="M48" s="32">
+      <c r="M49" s="32">
         <f t="shared" si="2"/>
         <v>2200</v>
       </c>
-      <c r="N48" s="32">
+      <c r="N49" s="32">
         <v>300</v>
       </c>
-      <c r="O48" s="32">
+      <c r="O49" s="32">
         <v>2300</v>
       </c>
-      <c r="P48" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q48" s="41">
+      <c r="P49" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q49" s="37">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="R48" s="42">
+      <c r="R49" s="38">
         <f t="shared" si="3"/>
         <v>0.24000000000000002</v>
       </c>
-      <c r="S48" s="41">
+      <c r="S49" s="37">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="T48" s="42">
+      <c r="T49" s="38">
         <f t="shared" si="4"/>
         <v>1.38</v>
       </c>
-      <c r="U48" s="42"/>
-    </row>
-    <row r="49" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="63">
-        <f>ROW(B49) - ROW($B$9)</f>
-        <v>40</v>
-      </c>
-      <c r="C49" s="49" t="s">
+      <c r="U49" s="38"/>
+    </row>
+    <row r="50" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="56">
+        <f>ROW(B50) - ROW($B$9)</f>
+        <v>41</v>
+      </c>
+      <c r="C50" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D49" s="49" t="s">
+      <c r="D50" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="49" t="s">
+      <c r="E50" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F49" s="69" t="s">
+      <c r="F50" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="G49" s="75" t="s">
+      <c r="G50" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="H49" s="69" t="s">
+      <c r="H50" s="62" t="s">
         <v>170</v>
       </c>
-      <c r="I49" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="J49" s="90" t="s">
+      <c r="I50" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="J50" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="K49" s="95">
+      <c r="K50" s="88">
         <v>1</v>
       </c>
-      <c r="L49" s="31">
+      <c r="L50" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M49" s="31">
+      <c r="M50" s="31">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N49" s="31">
+      <c r="N50" s="31">
         <v>12</v>
       </c>
-      <c r="O49" s="31">
+      <c r="O50" s="31">
         <v>110</v>
       </c>
-      <c r="P49" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q49" s="33">
+      <c r="P50" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q50" s="33">
         <v>0.86199999999999999</v>
       </c>
-      <c r="R49" s="34">
+      <c r="R50" s="34">
         <f t="shared" si="3"/>
         <v>10.343999999999999</v>
       </c>
-      <c r="S49" s="33">
+      <c r="S50" s="33">
         <v>0.74480000000000002</v>
       </c>
-      <c r="T49" s="34">
+      <c r="T50" s="34">
         <f t="shared" si="4"/>
         <v>81.927999999999997</v>
       </c>
-      <c r="U49" s="34"/>
-    </row>
-    <row r="50" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="63">
+      <c r="U50" s="34"/>
+    </row>
+    <row r="51" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="56">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="D50" s="52" t="s">
+      <c r="D51" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="E50" s="52" t="s">
+      <c r="E51" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="F50" s="68" t="s">
+      <c r="F51" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="G50" s="74" t="s">
+      <c r="G51" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="H50" s="68" t="s">
+      <c r="H51" s="61" t="s">
         <v>171</v>
       </c>
-      <c r="I50" s="74" t="s">
+      <c r="I51" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="J50" s="91" t="s">
+      <c r="J51" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="K50" s="94">
+      <c r="K51" s="87">
         <v>1</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L51" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M51" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N51" s="32">
         <v>10</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O51" s="32">
         <v>100</v>
       </c>
-      <c r="P50" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q50" s="41">
+      <c r="P51" s="36" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q51" s="37">
         <v>0.51200000000000001</v>
       </c>
-      <c r="R50" s="42">
+      <c r="R51" s="38">
         <f t="shared" si="3"/>
         <v>5.12</v>
       </c>
-      <c r="S50" s="41">
+      <c r="S51" s="37">
         <v>0.51200000000000001</v>
       </c>
-      <c r="T50" s="42">
+      <c r="T51" s="38">
         <f t="shared" si="4"/>
         <v>51.2</v>
       </c>
-      <c r="U50" s="42"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="63">
-        <f>ROW(B51) - ROW($B$9)</f>
-        <v>42</v>
-      </c>
-      <c r="C51" s="49" t="s">
+      <c r="U51" s="38"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="56">
+        <f>ROW(B52) - ROW($B$9)</f>
+        <v>43</v>
+      </c>
+      <c r="C52" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D51" s="49" t="s">
+      <c r="D52" s="42" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" s="69" t="s">
+      <c r="E52" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="F52" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="G51" s="75" t="s">
+      <c r="G52" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H51" s="69" t="s">
+      <c r="H52" s="62" t="s">
         <v>172</v>
       </c>
-      <c r="I51" s="49" t="s">
-        <v>261</v>
-      </c>
-      <c r="J51" s="90" t="s">
+      <c r="I52" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="J52" s="83" t="s">
         <v>210</v>
       </c>
-      <c r="K51" s="95">
+      <c r="K52" s="88">
         <v>2</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L52" s="31">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M52" s="31">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N52" s="31">
         <v>22</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O52" s="31">
         <v>210</v>
       </c>
-      <c r="P51" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q51" s="33">
+      <c r="P52" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q52" s="33">
         <v>0.3427</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R52" s="34">
         <f t="shared" si="3"/>
         <v>7.5394000000000005</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S52" s="33">
         <v>0.2777</v>
       </c>
-      <c r="T51" s="34">
+      <c r="T52" s="34">
         <f t="shared" si="4"/>
         <v>58.317</v>
       </c>
-      <c r="U51" s="34"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="63">
+      <c r="U52" s="34"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="56">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="52" t="s">
+      <c r="D53" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="E52" s="52" t="s">
-        <v>284</v>
-      </c>
-      <c r="F52" s="68" t="s">
+      <c r="E53" s="45" t="s">
+        <v>283</v>
+      </c>
+      <c r="F53" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="74" t="s">
+      <c r="G53" s="67" t="s">
         <v>212</v>
       </c>
-      <c r="H52" s="68" t="s">
+      <c r="H53" s="61" t="s">
         <v>173</v>
       </c>
-      <c r="I52" s="52" t="s">
-        <v>262</v>
-      </c>
-      <c r="J52" s="91" t="s">
+      <c r="I53" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="J53" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="K52" s="94">
+      <c r="K53" s="87">
         <v>1</v>
       </c>
-      <c r="L52" s="32">
+      <c r="L53" s="32">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M52" s="32">
+      <c r="M53" s="32">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N52" s="32">
+      <c r="N53" s="32">
         <v>12</v>
       </c>
-      <c r="O52" s="32">
+      <c r="O53" s="32">
         <v>110</v>
       </c>
-      <c r="P52" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q52" s="41">
+      <c r="P53" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q53" s="37">
         <v>0.4022</v>
       </c>
-      <c r="R52" s="42">
+      <c r="R53" s="38">
         <f t="shared" si="3"/>
         <v>4.8263999999999996</v>
       </c>
-      <c r="S52" s="41">
+      <c r="S53" s="37">
         <v>0.3427</v>
       </c>
-      <c r="T52" s="42">
+      <c r="T53" s="38">
         <f t="shared" si="4"/>
         <v>37.697000000000003</v>
       </c>
-      <c r="U52" s="42"/>
-    </row>
-    <row r="53" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="63">
-        <f>ROW(B53) - ROW($B$9)</f>
-        <v>44</v>
-      </c>
-      <c r="C53" s="49" t="s">
+      <c r="U53" s="38"/>
+    </row>
+    <row r="54" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="56">
+        <f>ROW(B54) - ROW($B$9)</f>
+        <v>45</v>
+      </c>
+      <c r="C54" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D53" s="49" t="s">
+      <c r="D54" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="E53" s="49" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" s="69" t="s">
+      <c r="E54" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="F54" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="G53" s="75" t="s">
+      <c r="G54" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="H53" s="69" t="s">
-        <v>285</v>
-      </c>
-      <c r="I53" s="75" t="s">
+      <c r="H54" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="I54" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="J53" s="90" t="s">
+      <c r="J54" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="K53" s="95">
+      <c r="K54" s="88">
         <v>1</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L54" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M54" s="31">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N54" s="31">
         <v>10</v>
       </c>
-      <c r="O53" s="31">
+      <c r="O54" s="31">
         <v>105</v>
       </c>
-      <c r="P53" s="37" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q53" s="33">
+      <c r="P54" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q54" s="33">
         <v>7.96</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R54" s="34">
         <f t="shared" si="3"/>
         <v>79.599999999999994</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S54" s="33">
         <v>7.96</v>
       </c>
-      <c r="T53" s="34">
+      <c r="T54" s="34">
         <f t="shared" si="4"/>
         <v>835.8</v>
       </c>
-      <c r="U53" s="34"/>
-    </row>
-    <row r="54" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="63">
+      <c r="U54" s="34"/>
+    </row>
+    <row r="55" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="56">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="52" t="s">
+      <c r="D55" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E54" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="F54" s="68" t="s">
+      <c r="E55" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="F55" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="G54" s="74" t="s">
+      <c r="G55" s="67" t="s">
         <v>210</v>
       </c>
-      <c r="H54" s="68" t="s">
+      <c r="H55" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="I54" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="J54" s="91" t="s">
+      <c r="I55" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="J55" s="84" t="s">
         <v>212</v>
       </c>
-      <c r="K54" s="94">
+      <c r="K55" s="87">
         <v>5</v>
       </c>
-      <c r="L54" s="32">
+      <c r="L55" s="32">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M55" s="32">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="N54" s="32">
+      <c r="N55" s="32">
         <v>55</v>
       </c>
-      <c r="O54" s="32">
+      <c r="O55" s="32">
         <v>510</v>
       </c>
-      <c r="P54" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q54" s="41">
+      <c r="P55" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q55" s="37">
         <v>0.42380000000000001</v>
       </c>
-      <c r="R54" s="42">
+      <c r="R55" s="38">
         <f t="shared" si="3"/>
         <v>23.309000000000001</v>
       </c>
-      <c r="S54" s="41">
+      <c r="S55" s="37">
         <v>0.36609999999999998</v>
       </c>
-      <c r="T54" s="42">
+      <c r="T55" s="38">
         <f t="shared" si="4"/>
         <v>186.71099999999998</v>
       </c>
-      <c r="U54" s="42"/>
-    </row>
-    <row r="55" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="63">
-        <f>ROW(B55) - ROW($B$9)</f>
-        <v>46</v>
-      </c>
-      <c r="C55" s="49" t="s">
+      <c r="U55" s="38"/>
+    </row>
+    <row r="56" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="56">
+        <f>ROW(B56) - ROW($B$9)</f>
+        <v>47</v>
+      </c>
+      <c r="C56" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="D55" s="49" t="s">
+      <c r="D56" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="E55" s="49" t="s">
+      <c r="E56" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F55" s="69" t="s">
+      <c r="F56" s="62" t="s">
         <v>151</v>
       </c>
-      <c r="G55" s="75" t="s">
+      <c r="G56" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="H55" s="69" t="s">
+      <c r="H56" s="62" t="s">
         <v>175</v>
       </c>
-      <c r="I55" s="49" t="s">
-        <v>264</v>
-      </c>
-      <c r="J55" s="90" t="s">
+      <c r="I56" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="J56" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="K55" s="95">
+      <c r="K56" s="88">
         <v>1</v>
       </c>
-      <c r="L55" s="31">
+      <c r="L56" s="31">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M55" s="31">
+      <c r="M56" s="31">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N55" s="31">
+      <c r="N56" s="31">
         <v>12</v>
       </c>
-      <c r="O55" s="31">
+      <c r="O56" s="31">
         <v>105</v>
       </c>
-      <c r="P55" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q55" s="33">
+      <c r="P56" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q56" s="33">
         <v>0.30380000000000001</v>
       </c>
-      <c r="R55" s="34">
+      <c r="R56" s="34">
         <f t="shared" si="3"/>
         <v>3.6456</v>
       </c>
-      <c r="S55" s="33">
+      <c r="S56" s="33">
         <v>0.21079999999999999</v>
       </c>
-      <c r="T55" s="34">
+      <c r="T56" s="34">
         <f t="shared" si="4"/>
         <v>22.134</v>
       </c>
-      <c r="U55" s="34"/>
-    </row>
-    <row r="56" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="77">
+      <c r="U56" s="34"/>
+    </row>
+    <row r="57" spans="1:21" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="70">
         <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="C56" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="D56" s="78" t="s">
+      <c r="D57" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="E56" s="78" t="s">
+      <c r="E57" s="71" t="s">
         <v>211</v>
       </c>
-      <c r="F56" s="79" t="s">
+      <c r="F57" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="G56" s="80" t="s">
+      <c r="G57" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="H56" s="79" t="s">
+      <c r="H57" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="I56" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="J56" s="79" t="s">
-        <v>222</v>
-      </c>
-      <c r="K56" s="109">
+      <c r="I57" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="J57" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="K57" s="101">
         <v>1</v>
       </c>
-      <c r="L56" s="81">
+      <c r="L57" s="74">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M56" s="81">
+      <c r="M57" s="74">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="N56" s="81">
+      <c r="N57" s="74">
         <v>15</v>
       </c>
-      <c r="O56" s="81">
+      <c r="O57" s="74">
         <v>110</v>
       </c>
-      <c r="P56" s="110" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q56" s="96">
+      <c r="P57" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q57" s="89">
         <v>0.1221</v>
       </c>
-      <c r="R56" s="97">
+      <c r="R57" s="90">
         <f t="shared" si="3"/>
         <v>1.8314999999999999</v>
       </c>
-      <c r="S56" s="96">
+      <c r="S57" s="89">
         <v>0.1008</v>
       </c>
-      <c r="T56" s="97">
+      <c r="T57" s="90">
         <f t="shared" si="4"/>
         <v>11.088000000000001</v>
       </c>
-      <c r="U56" s="97"/>
-    </row>
-    <row r="57" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="82"/>
-      <c r="C57" s="83" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="84"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="86"/>
-      <c r="G57" s="86"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="86"/>
-      <c r="K57" s="87"/>
-      <c r="L57" s="87"/>
-      <c r="M57" s="87"/>
-      <c r="N57" s="88"/>
-      <c r="O57" s="43" t="s">
-        <v>289</v>
-      </c>
-      <c r="P57" s="44"/>
-      <c r="Q57" s="44"/>
-      <c r="R57" s="102">
-        <f>SUM(R10:R56)</f>
-        <v>267.10050000000012</v>
-      </c>
-      <c r="S57" s="105"/>
-      <c r="T57" s="102">
-        <f>SUM(T10:T56)</f>
-        <v>1825.8290000000002</v>
-      </c>
-      <c r="U57" s="99"/>
+      <c r="U57" s="90"/>
     </row>
     <row r="58" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="7" t="s">
+      <c r="B58" s="75"/>
+      <c r="C58" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="77"/>
+      <c r="E58" s="78"/>
+      <c r="F58" s="79"/>
+      <c r="G58" s="79"/>
+      <c r="H58" s="78"/>
+      <c r="I58" s="78"/>
+      <c r="J58" s="79"/>
+      <c r="K58" s="80"/>
+      <c r="L58" s="80"/>
+      <c r="M58" s="80"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="P58" s="104"/>
+      <c r="Q58" s="104"/>
+      <c r="R58" s="94">
+        <f>SUM(R10:R57)</f>
+        <v>267.60030000000012</v>
+      </c>
+      <c r="S58" s="97"/>
+      <c r="T58" s="94">
+        <f>SUM(T10:T57)</f>
+        <v>1828.809</v>
+      </c>
+      <c r="U58" s="91"/>
+    </row>
+    <row r="59" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="45"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="45"/>
-      <c r="N58" s="89"/>
-      <c r="O58" s="98" t="s">
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="39"/>
+      <c r="L59" s="39"/>
+      <c r="M59" s="39"/>
+      <c r="N59" s="82"/>
+      <c r="O59" s="109" t="s">
+        <v>289</v>
+      </c>
+      <c r="P59" s="110"/>
+      <c r="Q59" s="110"/>
+      <c r="R59" s="95">
+        <f>R58/10</f>
+        <v>26.760030000000011</v>
+      </c>
+      <c r="S59" s="98"/>
+      <c r="T59" s="95">
+        <f>T58/100</f>
+        <v>18.28809</v>
+      </c>
+      <c r="U59" s="92"/>
+    </row>
+    <row r="60" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O60" s="103" t="s">
+        <v>287</v>
+      </c>
+      <c r="P60" s="104"/>
+      <c r="Q60" s="104"/>
+      <c r="R60" s="95">
+        <v>15.6</v>
+      </c>
+      <c r="S60" s="98"/>
+      <c r="T60" s="95">
+        <v>84.3</v>
+      </c>
+      <c r="U60" s="92"/>
+    </row>
+    <row r="61" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O61" s="103" t="s">
         <v>290</v>
       </c>
-      <c r="P58" s="46"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="103">
-        <f>R57/10</f>
-        <v>26.710050000000013</v>
-      </c>
-      <c r="S58" s="106"/>
-      <c r="T58" s="103">
-        <f>T57/100</f>
-        <v>18.258290000000002</v>
-      </c>
-      <c r="U58" s="100"/>
-    </row>
-    <row r="59" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O59" s="43" t="s">
-        <v>288</v>
-      </c>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
-      <c r="R59" s="103">
-        <v>15.6</v>
-      </c>
-      <c r="S59" s="106"/>
-      <c r="T59" s="103">
-        <v>84.3</v>
-      </c>
-      <c r="U59" s="100"/>
-    </row>
-    <row r="60" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O60" s="43" t="s">
-        <v>291</v>
-      </c>
-      <c r="P60" s="44"/>
-      <c r="Q60" s="44"/>
-      <c r="R60" s="104">
-        <f>SUM(R58:R59)</f>
-        <v>42.310050000000011</v>
-      </c>
-      <c r="S60" s="107"/>
-      <c r="T60" s="104">
-        <f>SUM(T58:T59)</f>
-        <v>102.55829</v>
-      </c>
-      <c r="U60" s="101"/>
+      <c r="P61" s="104"/>
+      <c r="Q61" s="104"/>
+      <c r="R61" s="96">
+        <f>SUM(R59:R60)</f>
+        <v>42.360030000000009</v>
+      </c>
+      <c r="S61" s="99"/>
+      <c r="T61" s="96">
+        <f>SUM(T59:T60)</f>
+        <v>102.58808999999999</v>
+      </c>
+      <c r="U61" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="O59:Q59"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="O60:Q60"/>
+    <mergeCell ref="O61:Q61"/>
     <mergeCell ref="U3:U8"/>
     <mergeCell ref="T2:U2"/>
-    <mergeCell ref="O57:Q57"/>
     <mergeCell ref="O58:Q58"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="O59:Q59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="P30" r:id="rId1" xr:uid="{2F7ACCE1-6330-4FB8-8E97-307E3319C2DE}"/>
@@ -5683,31 +5778,32 @@
     <hyperlink ref="P33" r:id="rId20" xr:uid="{062A632F-F1EB-4EB4-9D86-5BE7FA6F6DEB}"/>
     <hyperlink ref="P34" r:id="rId21" xr:uid="{E7F7B3C8-9A79-4316-957C-7140C5ACF4B9}"/>
     <hyperlink ref="P35" r:id="rId22" xr:uid="{1E45DDAB-804E-4CC3-BD40-0EBB99F81712}"/>
-    <hyperlink ref="P36" r:id="rId23" xr:uid="{89232A72-9254-4A2F-8534-FB7B74758559}"/>
-    <hyperlink ref="P37" r:id="rId24" xr:uid="{3948AA46-8D94-453A-969E-5BE874AF0204}"/>
-    <hyperlink ref="P38" r:id="rId25" xr:uid="{166ADBD4-943F-4ECC-95E2-D4E57A9202DA}"/>
-    <hyperlink ref="P39" r:id="rId26" xr:uid="{4131DE7B-77EF-497B-932D-D11A51BAFAD8}"/>
-    <hyperlink ref="P40" r:id="rId27" xr:uid="{EE42F985-F887-481A-ABAD-3892E9DF1783}"/>
-    <hyperlink ref="P41" r:id="rId28" xr:uid="{4723D86B-1885-45F4-8D16-D3E5F7BACAEA}"/>
-    <hyperlink ref="P42" r:id="rId29" xr:uid="{50402008-E888-42E5-B37B-4C1CA46E922C}"/>
-    <hyperlink ref="P43" r:id="rId30" xr:uid="{02C490EA-37FA-4E68-A4A5-44A8D3ED5B48}"/>
-    <hyperlink ref="P45" r:id="rId31" xr:uid="{1EF6C760-C341-401C-9175-F7D45AC47B77}"/>
-    <hyperlink ref="P46" r:id="rId32" xr:uid="{591682BE-520A-4F3D-8A8A-ABC5F9E8F6DE}"/>
-    <hyperlink ref="P47" r:id="rId33" xr:uid="{99988462-F1C8-44B4-96C3-1B88F5BF930D}"/>
-    <hyperlink ref="P48" r:id="rId34" xr:uid="{775129CE-5F45-483A-BA6C-9CDD4367CEB5}"/>
-    <hyperlink ref="P49" r:id="rId35" xr:uid="{5659A1E3-D32B-4B55-87D4-9B5A95CCA83F}"/>
-    <hyperlink ref="P50" r:id="rId36" xr:uid="{0E564FE6-FFFB-4AFD-AE93-4B98F9805F61}"/>
-    <hyperlink ref="P51" r:id="rId37" xr:uid="{D03B4D86-7CD8-4450-BC82-487F997A38AB}"/>
-    <hyperlink ref="P52" r:id="rId38" xr:uid="{C6B26088-BEA0-4425-9AF3-1A2B5444A64E}"/>
-    <hyperlink ref="P53" r:id="rId39" xr:uid="{B0F6DBA4-47C8-421E-8D8D-E7CDDAA9B8E7}"/>
-    <hyperlink ref="P54" r:id="rId40" xr:uid="{845F5956-7C23-4391-9FD5-6E93246239D6}"/>
-    <hyperlink ref="P55" r:id="rId41" xr:uid="{2EF96914-BBAD-4919-B0A3-9757DF18FBAA}"/>
-    <hyperlink ref="P56" r:id="rId42" xr:uid="{6BD0D022-CC4B-4A90-956C-EA7C7D09A4BB}"/>
+    <hyperlink ref="P37" r:id="rId23" xr:uid="{89232A72-9254-4A2F-8534-FB7B74758559}"/>
+    <hyperlink ref="P38" r:id="rId24" xr:uid="{3948AA46-8D94-453A-969E-5BE874AF0204}"/>
+    <hyperlink ref="P39" r:id="rId25" xr:uid="{166ADBD4-943F-4ECC-95E2-D4E57A9202DA}"/>
+    <hyperlink ref="P40" r:id="rId26" xr:uid="{4131DE7B-77EF-497B-932D-D11A51BAFAD8}"/>
+    <hyperlink ref="P41" r:id="rId27" xr:uid="{EE42F985-F887-481A-ABAD-3892E9DF1783}"/>
+    <hyperlink ref="P42" r:id="rId28" xr:uid="{4723D86B-1885-45F4-8D16-D3E5F7BACAEA}"/>
+    <hyperlink ref="P43" r:id="rId29" xr:uid="{50402008-E888-42E5-B37B-4C1CA46E922C}"/>
+    <hyperlink ref="P44" r:id="rId30" xr:uid="{02C490EA-37FA-4E68-A4A5-44A8D3ED5B48}"/>
+    <hyperlink ref="P46" r:id="rId31" xr:uid="{1EF6C760-C341-401C-9175-F7D45AC47B77}"/>
+    <hyperlink ref="P47" r:id="rId32" xr:uid="{591682BE-520A-4F3D-8A8A-ABC5F9E8F6DE}"/>
+    <hyperlink ref="P48" r:id="rId33" xr:uid="{99988462-F1C8-44B4-96C3-1B88F5BF930D}"/>
+    <hyperlink ref="P49" r:id="rId34" xr:uid="{775129CE-5F45-483A-BA6C-9CDD4367CEB5}"/>
+    <hyperlink ref="P50" r:id="rId35" xr:uid="{5659A1E3-D32B-4B55-87D4-9B5A95CCA83F}"/>
+    <hyperlink ref="P51" r:id="rId36" xr:uid="{0E564FE6-FFFB-4AFD-AE93-4B98F9805F61}"/>
+    <hyperlink ref="P52" r:id="rId37" xr:uid="{D03B4D86-7CD8-4450-BC82-487F997A38AB}"/>
+    <hyperlink ref="P53" r:id="rId38" xr:uid="{C6B26088-BEA0-4425-9AF3-1A2B5444A64E}"/>
+    <hyperlink ref="P54" r:id="rId39" xr:uid="{B0F6DBA4-47C8-421E-8D8D-E7CDDAA9B8E7}"/>
+    <hyperlink ref="P55" r:id="rId40" xr:uid="{845F5956-7C23-4391-9FD5-6E93246239D6}"/>
+    <hyperlink ref="P56" r:id="rId41" xr:uid="{2EF96914-BBAD-4919-B0A3-9757DF18FBAA}"/>
+    <hyperlink ref="P57" r:id="rId42" xr:uid="{6BD0D022-CC4B-4A90-956C-EA7C7D09A4BB}"/>
     <hyperlink ref="P27" r:id="rId43" xr:uid="{6F20BBBA-327D-49D2-8651-44DD5479D4F7}"/>
-    <hyperlink ref="P23" r:id="rId44" xr:uid="{D496978F-A56F-4B88-998E-B88C59397FE9}"/>
+    <hyperlink ref="P23" r:id="rId44" xr:uid="{9A445BA4-E19F-4F79-9207-C31C95F96585}"/>
+    <hyperlink ref="P36" r:id="rId45" xr:uid="{3128E03B-1874-41DC-B355-5921D175B75E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId45"/>
-  <drawing r:id="rId46"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>
+  <drawing r:id="rId47"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Bill of Materials-John_Main.xlsx
+++ b/Deliverables/BOM/Bill of Materials-John_Main.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-MatrixProject\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\JohnWollam-MatrixProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125E2DA5-DCC7-4888-879A-660E0F4D49B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -944,7 +943,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
@@ -1845,6 +1844,15 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
@@ -1872,15 +1880,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2217,7 +2216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2249,8 +2248,8 @@
       <c r="G1" s="30"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="112"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="105"/>
       <c r="L1" s="18"/>
       <c r="M1" s="18"/>
     </row>
@@ -2278,8 +2277,8 @@
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
       <c r="S2" s="10"/>
-      <c r="T2" s="107"/>
-      <c r="U2" s="108"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="111"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -2306,7 +2305,7 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-      <c r="U3" s="105"/>
+      <c r="U3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2333,7 +2332,7 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="106"/>
+      <c r="U4" s="109"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2360,7 +2359,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="106"/>
+      <c r="U5" s="109"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2383,7 +2382,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="106"/>
+      <c r="U6" s="109"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2406,7 +2405,7 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="106"/>
+      <c r="U7" s="109"/>
     </row>
     <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2429,7 +2428,7 @@
       <c r="R8" s="48"/>
       <c r="S8" s="48"/>
       <c r="T8" s="48"/>
-      <c r="U8" s="106"/>
+      <c r="U8" s="109"/>
     </row>
     <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -3591,25 +3590,25 @@
         <f t="shared" si="2"/>
         <v>700</v>
       </c>
-      <c r="N26" s="113" t="s">
+      <c r="N26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="O26" s="113" t="s">
+      <c r="O26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="P26" s="113" t="s">
+      <c r="P26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="Q26" s="113" t="s">
+      <c r="Q26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="R26" s="113" t="s">
+      <c r="R26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="S26" s="113" t="s">
+      <c r="S26" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="T26" s="113" t="s">
+      <c r="T26" s="103" t="s">
         <v>209</v>
       </c>
       <c r="U26" s="34"/>
@@ -5664,11 +5663,11 @@
       <c r="L58" s="80"/>
       <c r="M58" s="80"/>
       <c r="N58" s="81"/>
-      <c r="O58" s="103" t="s">
+      <c r="O58" s="106" t="s">
         <v>288</v>
       </c>
-      <c r="P58" s="104"/>
-      <c r="Q58" s="104"/>
+      <c r="P58" s="107"/>
+      <c r="Q58" s="107"/>
       <c r="R58" s="94">
         <f>SUM(R10:R57)</f>
         <v>267.60030000000012</v>
@@ -5697,11 +5696,11 @@
       <c r="L59" s="39"/>
       <c r="M59" s="39"/>
       <c r="N59" s="82"/>
-      <c r="O59" s="109" t="s">
+      <c r="O59" s="112" t="s">
         <v>289</v>
       </c>
-      <c r="P59" s="110"/>
-      <c r="Q59" s="110"/>
+      <c r="P59" s="113"/>
+      <c r="Q59" s="113"/>
       <c r="R59" s="95">
         <f>R58/10</f>
         <v>26.760030000000011</v>
@@ -5714,11 +5713,11 @@
       <c r="U59" s="92"/>
     </row>
     <row r="60" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O60" s="103" t="s">
+      <c r="O60" s="106" t="s">
         <v>287</v>
       </c>
-      <c r="P60" s="104"/>
-      <c r="Q60" s="104"/>
+      <c r="P60" s="107"/>
+      <c r="Q60" s="107"/>
       <c r="R60" s="95">
         <v>15.6</v>
       </c>
@@ -5729,11 +5728,11 @@
       <c r="U60" s="92"/>
     </row>
     <row r="61" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="O61" s="103" t="s">
+      <c r="O61" s="106" t="s">
         <v>290</v>
       </c>
-      <c r="P61" s="104"/>
-      <c r="Q61" s="104"/>
+      <c r="P61" s="107"/>
+      <c r="Q61" s="107"/>
       <c r="R61" s="96">
         <f>SUM(R59:R60)</f>
         <v>42.360030000000009</v>
@@ -5756,51 +5755,51 @@
     <mergeCell ref="O59:Q59"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="P30" r:id="rId1" xr:uid="{2F7ACCE1-6330-4FB8-8E97-307E3319C2DE}"/>
-    <hyperlink ref="P10" r:id="rId2" xr:uid="{2FD930C5-FD4D-4485-90FD-8F42F2FB86D7}"/>
-    <hyperlink ref="P11" r:id="rId3" xr:uid="{688A594C-DCDB-431E-8DB2-3B73EB820898}"/>
-    <hyperlink ref="P12" r:id="rId4" xr:uid="{6BEA14D3-818D-4150-AAF2-C8F29C4E446F}"/>
-    <hyperlink ref="P13" r:id="rId5" xr:uid="{3BC620E1-E1C4-4CB2-97F8-0D7A99A20BA6}"/>
-    <hyperlink ref="P14" r:id="rId6" xr:uid="{86CA8042-2DC3-473D-A979-72AA83514D52}"/>
-    <hyperlink ref="P15" r:id="rId7" xr:uid="{10F67B99-3057-42AF-9D42-570C3F0C60F9}"/>
-    <hyperlink ref="P16" r:id="rId8" xr:uid="{C60F0072-FB12-4DC1-A5ED-163CB541B5EE}"/>
-    <hyperlink ref="P17" r:id="rId9" xr:uid="{D6325761-9FC1-40D8-A82A-BE2228F64DD4}"/>
-    <hyperlink ref="P18" r:id="rId10" xr:uid="{FB501BA7-9DA3-4FB5-96C5-5C3DE4D94636}"/>
-    <hyperlink ref="P19" r:id="rId11" xr:uid="{52A5DA0D-4027-4FB3-9D9D-CCAE0B3978E9}"/>
-    <hyperlink ref="P20" r:id="rId12" xr:uid="{A040D7AB-FCEA-42F9-AA19-32A18DFCC9FD}"/>
-    <hyperlink ref="P21" r:id="rId13" xr:uid="{78C6F96A-EC11-4F4D-BEC2-D9CE6B61E957}"/>
-    <hyperlink ref="P22" r:id="rId14" xr:uid="{DCE2F2B0-D3E6-44CA-918D-195765810164}"/>
-    <hyperlink ref="P24" r:id="rId15" xr:uid="{EFF8AB1D-F8FF-44D4-AD07-A2579EB1243B}"/>
-    <hyperlink ref="P25" r:id="rId16" xr:uid="{01F791E4-771A-4DD8-A4EF-F9126473CB59}"/>
-    <hyperlink ref="P28" r:id="rId17" xr:uid="{BBAB8A3F-1C1F-4113-8688-4EF88392549D}"/>
-    <hyperlink ref="P29" r:id="rId18" xr:uid="{211E7481-A001-46F9-BD5F-2A77B5800AB3}"/>
-    <hyperlink ref="P32" r:id="rId19" xr:uid="{7CDD01B6-C01F-461B-9592-D9BA3EA621F2}"/>
-    <hyperlink ref="P33" r:id="rId20" xr:uid="{062A632F-F1EB-4EB4-9D86-5BE7FA6F6DEB}"/>
-    <hyperlink ref="P34" r:id="rId21" xr:uid="{E7F7B3C8-9A79-4316-957C-7140C5ACF4B9}"/>
-    <hyperlink ref="P35" r:id="rId22" xr:uid="{1E45DDAB-804E-4CC3-BD40-0EBB99F81712}"/>
-    <hyperlink ref="P37" r:id="rId23" xr:uid="{89232A72-9254-4A2F-8534-FB7B74758559}"/>
-    <hyperlink ref="P38" r:id="rId24" xr:uid="{3948AA46-8D94-453A-969E-5BE874AF0204}"/>
-    <hyperlink ref="P39" r:id="rId25" xr:uid="{166ADBD4-943F-4ECC-95E2-D4E57A9202DA}"/>
-    <hyperlink ref="P40" r:id="rId26" xr:uid="{4131DE7B-77EF-497B-932D-D11A51BAFAD8}"/>
-    <hyperlink ref="P41" r:id="rId27" xr:uid="{EE42F985-F887-481A-ABAD-3892E9DF1783}"/>
-    <hyperlink ref="P42" r:id="rId28" xr:uid="{4723D86B-1885-45F4-8D16-D3E5F7BACAEA}"/>
-    <hyperlink ref="P43" r:id="rId29" xr:uid="{50402008-E888-42E5-B37B-4C1CA46E922C}"/>
-    <hyperlink ref="P44" r:id="rId30" xr:uid="{02C490EA-37FA-4E68-A4A5-44A8D3ED5B48}"/>
-    <hyperlink ref="P46" r:id="rId31" xr:uid="{1EF6C760-C341-401C-9175-F7D45AC47B77}"/>
-    <hyperlink ref="P47" r:id="rId32" xr:uid="{591682BE-520A-4F3D-8A8A-ABC5F9E8F6DE}"/>
-    <hyperlink ref="P48" r:id="rId33" xr:uid="{99988462-F1C8-44B4-96C3-1B88F5BF930D}"/>
-    <hyperlink ref="P49" r:id="rId34" xr:uid="{775129CE-5F45-483A-BA6C-9CDD4367CEB5}"/>
-    <hyperlink ref="P50" r:id="rId35" xr:uid="{5659A1E3-D32B-4B55-87D4-9B5A95CCA83F}"/>
-    <hyperlink ref="P51" r:id="rId36" xr:uid="{0E564FE6-FFFB-4AFD-AE93-4B98F9805F61}"/>
-    <hyperlink ref="P52" r:id="rId37" xr:uid="{D03B4D86-7CD8-4450-BC82-487F997A38AB}"/>
-    <hyperlink ref="P53" r:id="rId38" xr:uid="{C6B26088-BEA0-4425-9AF3-1A2B5444A64E}"/>
-    <hyperlink ref="P54" r:id="rId39" xr:uid="{B0F6DBA4-47C8-421E-8D8D-E7CDDAA9B8E7}"/>
-    <hyperlink ref="P55" r:id="rId40" xr:uid="{845F5956-7C23-4391-9FD5-6E93246239D6}"/>
-    <hyperlink ref="P56" r:id="rId41" xr:uid="{2EF96914-BBAD-4919-B0A3-9757DF18FBAA}"/>
-    <hyperlink ref="P57" r:id="rId42" xr:uid="{6BD0D022-CC4B-4A90-956C-EA7C7D09A4BB}"/>
-    <hyperlink ref="P27" r:id="rId43" xr:uid="{6F20BBBA-327D-49D2-8651-44DD5479D4F7}"/>
-    <hyperlink ref="P23" r:id="rId44" xr:uid="{9A445BA4-E19F-4F79-9207-C31C95F96585}"/>
-    <hyperlink ref="P36" r:id="rId45" xr:uid="{3128E03B-1874-41DC-B355-5921D175B75E}"/>
+    <hyperlink ref="P30" r:id="rId1"/>
+    <hyperlink ref="P10" r:id="rId2"/>
+    <hyperlink ref="P11" r:id="rId3"/>
+    <hyperlink ref="P12" r:id="rId4"/>
+    <hyperlink ref="P13" r:id="rId5"/>
+    <hyperlink ref="P14" r:id="rId6"/>
+    <hyperlink ref="P15" r:id="rId7"/>
+    <hyperlink ref="P16" r:id="rId8"/>
+    <hyperlink ref="P17" r:id="rId9"/>
+    <hyperlink ref="P18" r:id="rId10"/>
+    <hyperlink ref="P19" r:id="rId11"/>
+    <hyperlink ref="P20" r:id="rId12"/>
+    <hyperlink ref="P21" r:id="rId13"/>
+    <hyperlink ref="P22" r:id="rId14"/>
+    <hyperlink ref="P24" r:id="rId15"/>
+    <hyperlink ref="P25" r:id="rId16"/>
+    <hyperlink ref="P28" r:id="rId17"/>
+    <hyperlink ref="P29" r:id="rId18"/>
+    <hyperlink ref="P32" r:id="rId19"/>
+    <hyperlink ref="P33" r:id="rId20"/>
+    <hyperlink ref="P34" r:id="rId21"/>
+    <hyperlink ref="P35" r:id="rId22"/>
+    <hyperlink ref="P37" r:id="rId23"/>
+    <hyperlink ref="P38" r:id="rId24"/>
+    <hyperlink ref="P39" r:id="rId25"/>
+    <hyperlink ref="P40" r:id="rId26"/>
+    <hyperlink ref="P41" r:id="rId27"/>
+    <hyperlink ref="P42" r:id="rId28"/>
+    <hyperlink ref="P43" r:id="rId29"/>
+    <hyperlink ref="P44" r:id="rId30"/>
+    <hyperlink ref="P46" r:id="rId31"/>
+    <hyperlink ref="P47" r:id="rId32"/>
+    <hyperlink ref="P48" r:id="rId33"/>
+    <hyperlink ref="P49" r:id="rId34"/>
+    <hyperlink ref="P50" r:id="rId35"/>
+    <hyperlink ref="P51" r:id="rId36"/>
+    <hyperlink ref="P52" r:id="rId37"/>
+    <hyperlink ref="P53" r:id="rId38"/>
+    <hyperlink ref="P54" r:id="rId39"/>
+    <hyperlink ref="P55" r:id="rId40"/>
+    <hyperlink ref="P56" r:id="rId41"/>
+    <hyperlink ref="P57" r:id="rId42"/>
+    <hyperlink ref="P27" r:id="rId43"/>
+    <hyperlink ref="P23" r:id="rId44"/>
+    <hyperlink ref="P36" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId46"/>

--- a/Deliverables/BOM/Bill of Materials-John_Main.xlsx
+++ b/Deliverables/BOM/Bill of Materials-John_Main.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="302">
   <si>
     <t>Component list</t>
   </si>
@@ -917,9 +917,6 @@
   </si>
   <si>
     <t xml:space="preserve">Custom Supplier </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urooj Is part Custom supplier se Quotation le len </t>
   </si>
   <si>
     <t>R12, R19, R20, R25, R26, RF3</t>
@@ -3919,19 +3916,21 @@
       <c r="P31" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="Q31" s="37"/>
+      <c r="Q31" s="37">
+        <v>0.83</v>
+      </c>
       <c r="R31" s="38">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="37"/>
+        <v>18.259999999999998</v>
+      </c>
+      <c r="S31" s="37">
+        <v>0.83</v>
+      </c>
       <c r="T31" s="38">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="100" t="s">
-        <v>296</v>
-      </c>
+        <v>170.15</v>
+      </c>
+      <c r="U31" s="100"/>
     </row>
     <row r="32" spans="1:21" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
@@ -4138,7 +4137,7 @@
         <v>26</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D35" s="44" t="s">
         <v>79</v>
@@ -4203,25 +4202,25 @@
         <v>27</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E36" s="44" t="s">
         <v>116</v>
       </c>
       <c r="F36" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="G36" s="69" t="s">
         <v>300</v>
-      </c>
-      <c r="G36" s="69" t="s">
-        <v>301</v>
       </c>
       <c r="H36" s="64" t="s">
         <v>156</v>
       </c>
       <c r="I36" s="44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J36" s="64" t="s">
         <v>191</v>
@@ -5670,12 +5669,12 @@
       <c r="Q58" s="107"/>
       <c r="R58" s="94">
         <f>SUM(R10:R57)</f>
-        <v>267.60030000000012</v>
+        <v>285.86030000000017</v>
       </c>
       <c r="S58" s="97"/>
       <c r="T58" s="94">
         <f>SUM(T10:T57)</f>
-        <v>1828.809</v>
+        <v>1998.9589999999998</v>
       </c>
       <c r="U58" s="91"/>
     </row>
@@ -5703,12 +5702,12 @@
       <c r="Q59" s="113"/>
       <c r="R59" s="95">
         <f>R58/10</f>
-        <v>26.760030000000011</v>
+        <v>28.586030000000015</v>
       </c>
       <c r="S59" s="98"/>
       <c r="T59" s="95">
         <f>T58/100</f>
-        <v>18.28809</v>
+        <v>19.98959</v>
       </c>
       <c r="U59" s="92"/>
     </row>
@@ -5735,12 +5734,12 @@
       <c r="Q61" s="107"/>
       <c r="R61" s="96">
         <f>SUM(R59:R60)</f>
-        <v>42.360030000000009</v>
+        <v>44.186030000000017</v>
       </c>
       <c r="S61" s="99"/>
       <c r="T61" s="96">
         <f>SUM(T59:T60)</f>
-        <v>102.58808999999999</v>
+        <v>104.28959</v>
       </c>
       <c r="U61" s="93"/>
     </row>
